--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2021_aysen.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2021_aysen.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 19:46</t>
+    <t xml:space="preserve">2026-09-09 22:34</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2021_aysen.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2021_aysen.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 22:34</t>
+    <t xml:space="preserve">2026-09-12 19:50</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2021_aysen.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2021_aysen.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-12 19:50</t>
+    <t xml:space="preserve">2026-09-24 00:28</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2021_aysen.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2021_aysen.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:28</t>
+    <t xml:space="preserve">2026-09-27 23:11</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -508,7 +508,7 @@
         <v>2021</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>12.94</v>
+        <v>129.44</v>
       </c>
     </row>
     <row r="3">
@@ -525,7 +525,7 @@
         <v>2021</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>4.25</v>
+        <v>42.51</v>
       </c>
     </row>
     <row r="4">
@@ -542,7 +542,7 @@
         <v>2021</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>4.16</v>
+        <v>41.55</v>
       </c>
     </row>
     <row r="5">
@@ -559,7 +559,7 @@
         <v>2021</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>4.04</v>
+        <v>40.36</v>
       </c>
     </row>
     <row r="6">
@@ -576,7 +576,7 @@
         <v>2021</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.33</v>
+        <v>3.35</v>
       </c>
     </row>
     <row r="7">
@@ -593,7 +593,7 @@
         <v>2021</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>-0.19</v>
+        <v>-1.94</v>
       </c>
     </row>
     <row r="8">
@@ -610,7 +610,7 @@
         <v>2021</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>-0.34</v>
+        <v>-3.42</v>
       </c>
     </row>
     <row r="9">
@@ -627,7 +627,7 @@
         <v>2021</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>-0.58</v>
+        <v>-5.84</v>
       </c>
     </row>
     <row r="10">
@@ -644,7 +644,7 @@
         <v>2021</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>-1.94</v>
+        <v>-19.43</v>
       </c>
     </row>
     <row r="11">
@@ -661,7 +661,7 @@
         <v>2021</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>-2.39</v>
+        <v>-23.85</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2021_aysen.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2021_aysen.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 23:11</t>
+    <t xml:space="preserve">2026-10-01 20:57</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2021_aysen.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2021_aysen.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 20:57</t>
+    <t xml:space="preserve">2026-10-02 13:29</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2021_aysen.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2021_aysen.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 13:29</t>
+    <t xml:space="preserve">2026-10-04 08:15</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2021_aysen.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2021_aysen.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 08:15</t>
+    <t xml:space="preserve">2026-10-05 08:21</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
